--- a/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
+++ b/nr-doc-core-medication/ig/StructureDefinition-fr-core-medication-statement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T12:31:13+00:00</t>
+    <t>2026-10-15T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1141,7 +1141,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260619134041</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-human-substance-administration-site-cisis|20260916095453</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -1168,7 +1168,7 @@
     <t>EDQM - Standard terms / classe ROA (0.4.0.127.0.16.1.1.2.1)</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-edqm|2.2.0</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-edqm-route|2.2.0</t>
   </si>
   <si>
     <t>Dosage.route</t>
